--- a/stacked_model/results/validation/deposition_model_controls_to_deposition_summary.xlsx
+++ b/stacked_model/results/validation/deposition_model_controls_to_deposition_summary.xlsx
@@ -562,40 +562,40 @@
         <v>1900</v>
       </c>
       <c r="H2" t="n">
-        <v>3.432880675296015</v>
+        <v>3.443256318928505</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3817542260411853</v>
+        <v>0.37447001959853</v>
       </c>
       <c r="J2" t="n">
-        <v>4.582308598926443</v>
+        <v>4.603525284041718</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5112934295468461</v>
+        <v>0.5008180569741756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.772869326990449</v>
+        <v>0.7725109785490014</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06071646363784602</v>
+        <v>0.05648824630631295</v>
       </c>
       <c r="N2" t="n">
-        <v>0.866842105263158</v>
+        <v>0.8689473684210527</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05535642480099032</v>
+        <v>0.0563884711222476</v>
       </c>
       <c r="P2" t="n">
-        <v>3.126582970936398</v>
+        <v>3.193334177728245</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4932695266230907</v>
+        <v>0.6271261990191498</v>
       </c>
       <c r="R2" t="n">
-        <v>-117.5383180775372</v>
+        <v>-117.4092706075031</v>
       </c>
       <c r="S2" t="n">
-        <v>3.962128563784979</v>
+        <v>4.481342632593394</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -635,40 +635,40 @@
         <v>1900</v>
       </c>
       <c r="H3" t="n">
-        <v>3.434099098131329</v>
+        <v>3.443519805465228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3809099008571974</v>
+        <v>0.3747278172905925</v>
       </c>
       <c r="J3" t="n">
-        <v>4.583844104862155</v>
+        <v>4.60370779712007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5104247323576646</v>
+        <v>0.5009692811106323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7727342490364975</v>
+        <v>0.7724913615115532</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06062929920386277</v>
+        <v>0.05650392716020053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8742105263157895</v>
+        <v>0.8757894736842107</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05350774476190659</v>
+        <v>0.05237315719479097</v>
       </c>
       <c r="P3" t="n">
-        <v>3.08771418107404</v>
+        <v>3.04977555071663</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6307155765447575</v>
+        <v>0.328485607930392</v>
       </c>
       <c r="R3" t="n">
-        <v>-117.4315592994587</v>
+        <v>-117.3997209991836</v>
       </c>
       <c r="S3" t="n">
-        <v>4.185994643375805</v>
+        <v>4.508353374855829</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -708,40 +708,40 @@
         <v>1900</v>
       </c>
       <c r="H4" t="n">
-        <v>3.434099096484621</v>
+        <v>3.443520443705095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3809100847031243</v>
+        <v>0.3747289543154171</v>
       </c>
       <c r="J4" t="n">
-        <v>4.583844181084598</v>
+        <v>4.603709179861533</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5104247950657705</v>
+        <v>0.5009709940895716</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7727342424964155</v>
+        <v>0.7724912445534449</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06062930367018866</v>
+        <v>0.05650391094461293</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8742105263157895</v>
+        <v>0.8757894736842107</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05350774476190659</v>
+        <v>0.05237315719479097</v>
       </c>
       <c r="P4" t="n">
-        <v>3.087743019916063</v>
+        <v>3.049784634498774</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6308677110760262</v>
+        <v>0.3285048979265214</v>
       </c>
       <c r="R4" t="n">
-        <v>-117.4315592993045</v>
+        <v>-117.3997210017015</v>
       </c>
       <c r="S4" t="n">
-        <v>4.185994643369099</v>
+        <v>4.5083533768298</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>1e-06</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -781,40 +781,40 @@
         <v>1900</v>
       </c>
       <c r="H5" t="n">
-        <v>3.457110590144142</v>
+        <v>3.466968679090963</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4490449307875504</v>
+        <v>0.4052435412929845</v>
       </c>
       <c r="J5" t="n">
-        <v>4.612595140747029</v>
+        <v>4.637947152852727</v>
       </c>
       <c r="K5" t="n">
-        <v>0.587454504284259</v>
+        <v>0.5433693492409143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7692051492531198</v>
+        <v>0.7687568292336757</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0686286224882363</v>
+        <v>0.0606380880388891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8652631578947368</v>
+        <v>0.8742105263157895</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05790938199690138</v>
+        <v>0.05403342537466495</v>
       </c>
       <c r="P5" t="n">
-        <v>3.155544749142379</v>
+        <v>3.061240351787645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.527579734878287</v>
+        <v>0.3307846814051329</v>
       </c>
       <c r="R5" t="n">
-        <v>-117.4323476741037</v>
+        <v>-117.3585269039338</v>
       </c>
       <c r="S5" t="n">
-        <v>4.103928229387479</v>
+        <v>4.500477716705376</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
         <v>50</v>
@@ -854,40 +854,40 @@
         <v>1900</v>
       </c>
       <c r="H6" t="n">
-        <v>3.458454480095515</v>
+        <v>3.479339618324667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4487382402104824</v>
+        <v>0.4163103875751053</v>
       </c>
       <c r="J6" t="n">
-        <v>4.614247264107965</v>
+        <v>4.656564089468655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5870166113878141</v>
+        <v>0.5748975750729397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7690543916547915</v>
+        <v>0.7666466026211372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06859519558418599</v>
+        <v>0.06362838395544883</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8726315789473685</v>
+        <v>0.866842105263158</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05559844074386812</v>
+        <v>0.05953871334323512</v>
       </c>
       <c r="P6" t="n">
-        <v>3.104090027432973</v>
+        <v>3.232129648954282</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6389668365809775</v>
+        <v>0.6546710239680206</v>
       </c>
       <c r="R6" t="n">
-        <v>-117.3252903603542</v>
+        <v>-117.3268295568308</v>
       </c>
       <c r="S6" t="n">
-        <v>4.318329650723205</v>
+        <v>4.541118992618192</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -927,40 +927,40 @@
         <v>1900</v>
       </c>
       <c r="H7" t="n">
-        <v>3.458454218823177</v>
+        <v>3.483909969088897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4487352424135821</v>
+        <v>0.4246595518964142</v>
       </c>
       <c r="J7" t="n">
-        <v>4.614247521194718</v>
+        <v>4.660974224435389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5870150289264077</v>
+        <v>0.5838047743844124</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7690543899533079</v>
+        <v>0.766149739575976</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06859499507387437</v>
+        <v>0.06442021271485697</v>
       </c>
       <c r="N7" t="n">
         <v>0.8726315789473685</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05559844074386812</v>
+        <v>0.05685523180574305</v>
       </c>
       <c r="P7" t="n">
-        <v>3.104060854518174</v>
+        <v>3.127557529657686</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6388151488641017</v>
+        <v>0.5776619374061419</v>
       </c>
       <c r="R7" t="n">
-        <v>-117.3252903615404</v>
+        <v>-117.2591759224323</v>
       </c>
       <c r="S7" t="n">
-        <v>4.318329648399748</v>
+        <v>4.672546843451236</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F8" t="n">
         <v>50</v>
@@ -1000,40 +1000,40 @@
         <v>1900</v>
       </c>
       <c r="H8" t="n">
-        <v>3.670820332096605</v>
+        <v>3.709754758002719</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3995629997910594</v>
+        <v>0.358685722928652</v>
       </c>
       <c r="J8" t="n">
-        <v>4.775948621903612</v>
+        <v>4.857123097334653</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5251891246767287</v>
+        <v>0.486977141881412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7524883281363782</v>
+        <v>0.7468854196085399</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06821914360377973</v>
+        <v>0.05963599165562142</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8810526315789473</v>
+        <v>0.8742105263157895</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05296350756498142</v>
+        <v>0.05324295817662904</v>
       </c>
       <c r="P8" t="n">
-        <v>2.980169837668918</v>
+        <v>2.998128722408036</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1237890851413548</v>
+        <v>0.1158808755357519</v>
       </c>
       <c r="R8" t="n">
-        <v>-122.3662119709173</v>
+        <v>-122.1405651078226</v>
       </c>
       <c r="S8" t="n">
-        <v>4.011924055063536</v>
+        <v>3.850572894087481</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
@@ -1073,40 +1073,40 @@
         <v>1900</v>
       </c>
       <c r="H9" t="n">
-        <v>3.670820395704882</v>
+        <v>3.709754976117901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3995636388995941</v>
+        <v>0.358685335242283</v>
       </c>
       <c r="J9" t="n">
-        <v>4.775948760854281</v>
+        <v>4.857123374279075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5251903644162843</v>
+        <v>0.4869758860048832</v>
       </c>
       <c r="L9" t="n">
-        <v>0.752488301954079</v>
+        <v>0.7468853374680779</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06821923166181193</v>
+        <v>0.0596362513565185</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8810526315789473</v>
+        <v>0.8615789473684211</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05296350756498142</v>
+        <v>0.05671834799186137</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98017036892907</v>
+        <v>3.005838608488958</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1237900792065926</v>
+        <v>0.1271674381191973</v>
       </c>
       <c r="R9" t="n">
-        <v>-122.3662119712071</v>
+        <v>-122.1405650914613</v>
       </c>
       <c r="S9" t="n">
-        <v>4.011924055071219</v>
+        <v>3.850572894364687</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -1146,40 +1146,40 @@
         <v>1900</v>
       </c>
       <c r="H10" t="n">
-        <v>3.671594150557759</v>
+        <v>3.709755122701998</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4008066414970204</v>
+        <v>0.358685014471916</v>
       </c>
       <c r="J10" t="n">
-        <v>4.776648927858435</v>
+        <v>4.85712349434068</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5261482362909006</v>
+        <v>0.4869767649416206</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7523780846650052</v>
+        <v>0.7468853778091347</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0685209380203316</v>
+        <v>0.05963597538359333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8705263157894736</v>
+        <v>0.8742105263157895</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05391559411127086</v>
+        <v>0.05324295817662904</v>
       </c>
       <c r="P10" t="n">
-        <v>2.985768376302781</v>
+        <v>2.9981282035874</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1333527887281296</v>
+        <v>0.1158797563129038</v>
       </c>
       <c r="R10" t="n">
-        <v>-122.3663589612465</v>
+        <v>-122.140565102521</v>
       </c>
       <c r="S10" t="n">
-        <v>4.011686711005654</v>
+        <v>3.850572893695601</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
@@ -1219,40 +1219,40 @@
         <v>1900</v>
       </c>
       <c r="H11" t="n">
-        <v>3.677320917928911</v>
+        <v>3.709755171468339</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4389954582370614</v>
+        <v>0.3586858033445913</v>
       </c>
       <c r="J11" t="n">
-        <v>4.781164466452669</v>
+        <v>4.857123694841752</v>
       </c>
       <c r="K11" t="n">
-        <v>0.583129904906736</v>
+        <v>0.4869775985599932</v>
       </c>
       <c r="L11" t="n">
-        <v>0.751245479743699</v>
+        <v>0.7468853500064122</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07385870867329235</v>
+        <v>0.05963608800519114</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8815789473684209</v>
+        <v>0.8615789473684211</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05454367717498837</v>
+        <v>0.05671834799186137</v>
       </c>
       <c r="P11" t="n">
-        <v>2.981541677546098</v>
+        <v>3.005838788492237</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1292963713287512</v>
+        <v>0.1271669650004434</v>
       </c>
       <c r="R11" t="n">
-        <v>-122.3317478004683</v>
+        <v>-122.1405651003559</v>
       </c>
       <c r="S11" t="n">
-        <v>4.011489526008674</v>
+        <v>3.850572895599543</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1292,40 +1292,40 @@
         <v>1900</v>
       </c>
       <c r="H12" t="n">
-        <v>3.677321599751672</v>
+        <v>3.726592820092359</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4389973508746383</v>
+        <v>0.3696168453153781</v>
       </c>
       <c r="J12" t="n">
-        <v>4.781165064657404</v>
+        <v>4.885616616317524</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5831319988515832</v>
+        <v>0.5082680428752574</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7512454037644128</v>
+        <v>0.7437645315371816</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07385890952812468</v>
+        <v>0.06159917501785264</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8815789473684209</v>
+        <v>0.8731578947368422</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05454367717498837</v>
+        <v>0.05281653859187437</v>
       </c>
       <c r="P12" t="n">
-        <v>2.981541446415382</v>
+        <v>3.001018774913535</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1292958990526612</v>
+        <v>0.1147867811203453</v>
       </c>
       <c r="R12" t="n">
-        <v>-122.3317477996185</v>
+        <v>-122.1368894175959</v>
       </c>
       <c r="S12" t="n">
-        <v>4.011489526529976</v>
+        <v>3.848514315289827</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01</v>
+        <v>1e-06</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
@@ -1365,40 +1365,40 @@
         <v>1900</v>
       </c>
       <c r="H13" t="n">
-        <v>3.682517463270433</v>
+        <v>3.726593073091666</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4408544061738226</v>
+        <v>0.3696167492503292</v>
       </c>
       <c r="J13" t="n">
-        <v>4.790689556677747</v>
+        <v>4.885616791706679</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5863048546268791</v>
+        <v>0.5082679120012855</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7495205024284651</v>
+        <v>0.7437645271480272</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07852698652065895</v>
+        <v>0.06159908267756254</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8705263157894736</v>
+        <v>0.8731578947368422</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05647612619011706</v>
+        <v>0.05281653859187437</v>
       </c>
       <c r="P13" t="n">
-        <v>2.988752783737266</v>
+        <v>3.001019506540491</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1391451871592149</v>
+        <v>0.1147879577095422</v>
       </c>
       <c r="R13" t="n">
-        <v>-122.3059195239165</v>
+        <v>-122.1368894175088</v>
       </c>
       <c r="S13" t="n">
-        <v>4.043449691463575</v>
+        <v>3.848514315254851</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
